--- a/reports/telegram/aegis_daily_2026-09-02.xlsx
+++ b/reports/telegram/aegis_daily_2026-09-02.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV25"/>
+  <dimension ref="A1:AV19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -733,12 +733,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>R2-GNFC-IND-20260806-abf3d2</t>
+          <t>R2-PLTR-USA-20260810-caa9a7</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>GNFC_IND_20260806</t>
+          <t>PLTR_USA_20260810</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -775,7 +775,7 @@
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="3" t="n">
-        <v>80.5</v>
+        <v>79.2</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
@@ -783,24 +783,24 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>33.3</v>
+        <v>48.2</v>
       </c>
       <c r="Q2" s="3" t="n">
         <v>-0.8</v>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 34% · band HOLD→STRONG · 22d left · → STRONG BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 49% · band HOLD · 17d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr"/>
       <c r="U2" s="3" t="n">
-        <v>34.1</v>
+        <v>48.9</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -808,73 +808,73 @@
         </is>
       </c>
       <c r="W2" s="3" t="n">
-        <v>32.7</v>
+        <v>39.6</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AA2" s="3" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AB2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AC2" s="3" t="n">
-        <v>571.9</v>
+        <v>179.92</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>553.3</v>
+        <v>179.92</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>566.1799999999999</v>
+        <v>178.12</v>
       </c>
       <c r="AF2" s="3" t="n">
-        <v>577.62</v>
+        <v>181.72</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>537.59</v>
+        <v>169.12</v>
       </c>
       <c r="AH2" s="3" t="n">
-        <v>-2.84</v>
+        <v>-6</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>640.53</v>
+        <v>201.51</v>
       </c>
       <c r="AJ2" s="3" t="n">
-        <v>15.77</v>
+        <v>12</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>709.16</v>
+        <v>223.1</v>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>28.17</v>
+        <v>24</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>582.55</v>
+        <v>186.38</v>
       </c>
       <c r="AN2" s="3" t="n">
-        <v>-1.83</v>
+        <v>-3.47</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AP2" s="3" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AQ2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Value · Growth · Ai Hybrid</t>
+          <t>Value · Quality · Growth</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr"/>
@@ -886,19 +886,19 @@
       </c>
       <c r="AV2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:47</t>
+          <t>2026-09-02 12:28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>R2-ADANIENT-IND-20260902-60b571</t>
+          <t>R2-INCY-USA-20260902-924c1b</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ADANIENT_IND_20260902</t>
+          <t>INCY_USA_20260902</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -929,44 +929,44 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +57.0pp alpha</t>
+          <t>→ PLTR · +12.5pp alpha</t>
         </is>
       </c>
       <c r="J3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="n">
-        <v>52</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>🔴</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>20.3</v>
+        <v>48.2</v>
       </c>
       <c r="Q3" s="3" t="n">
         <v>-0.8</v>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank #13 · Conf 21% · band EXIT · 60d left · → EXIT (rotate to GNFC.NS)</t>
+          <t>🔴 AVOID · Rank #4 · Conf 49% · band HOLD · 60d left · → EXIT (rotate to PLTR)</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="n">
-        <v>21.1</v>
+        <v>48.9</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="W3" s="3" t="n">
-        <v>-24.3</v>
+        <v>27.1</v>
       </c>
       <c r="X3" s="3" t="n">
         <v>1</v>
@@ -994,40 +994,40 @@
         </is>
       </c>
       <c r="AC3" s="3" t="n">
-        <v>2863.9</v>
+        <v>125.01</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>2863.9</v>
+        <v>125.01</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>2835.26</v>
+        <v>123.76</v>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>2892.54</v>
+        <v>126.26</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>2720.7</v>
+        <v>118.76</v>
       </c>
       <c r="AH3" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>3093.01</v>
+        <v>135.01</v>
       </c>
       <c r="AJ3" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>3293.48</v>
+        <v>143.76</v>
       </c>
       <c r="AL3" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>3061.3</v>
+        <v>123.22</v>
       </c>
       <c r="AN3" s="3" t="n">
-        <v>-6.45</v>
+        <v>1.45</v>
       </c>
       <c r="AO3" s="3" t="inlineStr"/>
       <c r="AP3" s="3" t="n">
@@ -1038,29 +1038,29 @@
       </c>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
+          <t>Quality · Event Driven · Momentum</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr"/>
       <c r="AT3" s="3" t="inlineStr"/>
       <c r="AU3" s="3" t="n">
-        <v>56.95</v>
+        <v>12.5</v>
       </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:47</t>
+          <t>2026-09-02 12:28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>R1-SBIN-IND-20260821-686443</t>
+          <t>R2-OXY-USA-20260902-bcdb9b</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SBIN_IND_20260821</t>
+          <t>OXY_USA_20260902</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1070,45 +1070,65 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>→ PLTR · +13.9pp alpha</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K4" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr"/>
-      <c r="O4" s="3" t="inlineStr"/>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.1%) · Rank #2 · Conf 71% · momentum → · 91d left · → BUY</t>
+          <t>🔴 AVOID · Rank #8 · Conf 52% · band HOLD · 60d left · → EXIT (rotate to PLTR)</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr"/>
       <c r="U4" s="3" t="n">
-        <v>71</v>
+        <v>51.7</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1116,91 +1136,93 @@
         </is>
       </c>
       <c r="W4" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="X4" s="3" t="inlineStr"/>
+        <v>25.7</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y4" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA4" s="3" t="n">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AC4" s="3" t="n">
-        <v>1034.5</v>
+        <v>60.95</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>1048.699951171875</v>
+        <v>60.95</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>1001</v>
+        <v>60.34</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>1068</v>
+        <v>61.56</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>982.775</v>
+        <v>57.9</v>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>-6.29</v>
+        <v>-5</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>1117.26</v>
+        <v>65.83</v>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>6.54</v>
+        <v>8.01</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>1195.4682</v>
+        <v>70.09</v>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM4" s="3" t="n">
-        <v>1036</v>
+        <v>60.18</v>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="AO4" s="3" t="n">
-        <v>-1.35</v>
-      </c>
-      <c r="AP4" s="3" t="inlineStr"/>
-      <c r="AQ4" s="3" t="inlineStr"/>
-      <c r="AR4" s="3" t="inlineStr"/>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="n">
-        <v>5</v>
-      </c>
+        <v>1.28</v>
+      </c>
+      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AP4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Value · Momentum · Event Driven</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
       <c r="AU4" s="3" t="n">
-        <v>6.54</v>
+        <v>13.89</v>
       </c>
       <c r="AV4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:47</t>
+          <t>2026-09-02 12:28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>R1-BEL-IND-20260804-5cc411</t>
+          <t>R2-SNDK-USA-20260902-3414ff</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>BEL_IND_20260804</t>
+          <t>SNDK_USA_20260902</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1210,53 +1232,65 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>BEL</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Bharat Electronics</t>
-        </is>
-      </c>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>→ PLTR · +14.2pp alpha</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.8%) · Rank ↑ 8→3 · Conf 68% · momentum → · 91d left · → BUY</t>
+          <t>🔴 AVOID · Rank #10 · Conf 43% · band HOLD · 60d left · → EXIT (rotate to PLTR)</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="n">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1264,95 +1298,93 @@
         </is>
       </c>
       <c r="W5" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="X5" s="3" t="inlineStr"/>
+        <v>25.4</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y5" s="3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA5" s="3" t="n">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AC5" s="3" t="n">
-        <v>411.2</v>
+        <v>1536.87</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>388.7</v>
+        <v>1536.87</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>399</v>
+        <v>1521.5</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>423</v>
+        <v>1552.24</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>390.64</v>
+        <v>1460.03</v>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>0.5</v>
+        <v>-5</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>444.096</v>
+        <v>1659.82</v>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>14.25</v>
+        <v>8</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>475.18272</v>
+        <v>1767.4</v>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>22.25</v>
+        <v>15</v>
       </c>
       <c r="AM5" s="3" t="n">
-        <v>406.65</v>
+        <v>1566.7</v>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>5.79</v>
-      </c>
+        <v>-1.9</v>
+      </c>
+      <c r="AO5" s="3" t="inlineStr"/>
       <c r="AP5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Quality · Mean Reversion · Growth</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr"/>
+      <c r="AT5" s="3" t="inlineStr"/>
       <c r="AU5" s="3" t="n">
-        <v>14.25</v>
+        <v>14.2</v>
       </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:47</t>
+          <t>2026-09-02 12:28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>R1-WIPRO-IND-20260902-85c3d8</t>
+          <t>R2-XYZ-USA-20260902-cea5af</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>WIPRO_IND_20260902</t>
+          <t>XYZ_USA_20260902</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1362,45 +1394,65 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>→ PLTR · +66.0pp alpha</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K6" s="3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
-      <c r="N6" s="3" t="inlineStr"/>
-      <c r="O6" s="3" t="inlineStr"/>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.4%) · Rank #4 · Conf 70% · momentum → · 91d left · → BUY</t>
+          <t>🔴 AVOID · Rank #11 · Conf 30% · band EXIT · 60d left · → EXIT (rotate to PLTR)</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" s="3" t="n">
-        <v>70</v>
+        <v>29.9</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
@@ -1408,17 +1460,19 @@
         </is>
       </c>
       <c r="W6" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="X6" s="3" t="inlineStr"/>
+        <v>-26.5</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA6" s="3" t="n">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
@@ -1426,73 +1480,73 @@
         </is>
       </c>
       <c r="AC6" s="3" t="n">
-        <v>181.7</v>
+        <v>77.88</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>181.6999969482422</v>
+        <v>77.88</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>176</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>188</v>
+        <v>78.66</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>172.615</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>-5</v>
+        <v>-4.99</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>196.236</v>
+        <v>84.11</v>
       </c>
       <c r="AJ6" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>209.97252</v>
+        <v>89.56</v>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>15.56</v>
+        <v>15</v>
       </c>
       <c r="AM6" s="3" t="n">
-        <v>177.3</v>
+        <v>82.02</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="n">
-        <v>5</v>
-      </c>
+        <v>-5.05</v>
+      </c>
+      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AP6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
       <c r="AU6" s="3" t="n">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:47</t>
+          <t>2026-09-02 12:28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>R1-DABUR-IND-20260828-284464</t>
+          <t>R2-SW-USA-20260902-015fe2</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>DABUR_IND_20260828</t>
+          <t>SW_USA_20260902</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1502,45 +1556,65 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>SW</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>→ PLTR · +75.9pp alpha</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K7" s="3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank #7 · Conf 64% · momentum → · 91d left · → BUY</t>
+          <t>🔴 AVOID · Rank #15 · Conf 28% · band EXIT · 60d left · → EXIT (rotate to PLTR)</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="n">
-        <v>64</v>
+        <v>27.8</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -1548,91 +1622,93 @@
         </is>
       </c>
       <c r="W7" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="X7" s="3" t="inlineStr"/>
+        <v>-36.4</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y7" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA7" s="3" t="n">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AC7" s="3" t="n">
-        <v>384</v>
+        <v>45.43</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>385.1499938964844</v>
+        <v>45.43</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>372</v>
+        <v>44.98</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>396</v>
+        <v>45.88</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>364.8</v>
+        <v>43.16</v>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>-5.28</v>
+        <v>-5</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>414.72</v>
+        <v>49.06</v>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>7.68</v>
+        <v>7.99</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>443.7504000000001</v>
+        <v>52.24</v>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>15.21</v>
+        <v>14.99</v>
       </c>
       <c r="AM7" s="3" t="n">
-        <v>382.75</v>
+        <v>46.9</v>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AO7" s="3" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="AT7" s="3" t="n">
-        <v>5</v>
-      </c>
+        <v>-3.13</v>
+      </c>
+      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AP7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr"/>
+      <c r="AT7" s="3" t="inlineStr"/>
       <c r="AU7" s="3" t="n">
-        <v>7.68</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AV7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:47</t>
+          <t>2026-09-02 12:28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>R1-IRCTC-IND-20260804-9c1ab0</t>
+          <t>R1-PLTR-USA-20260902-1a2a27</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>IRCTC_IND_20260804</t>
+          <t>PLTR_USA_20260902</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1642,7 +1718,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1652,43 +1728,49 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>IRCTC</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>IRCTC</t>
-        </is>
-      </c>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="M8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr"/>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.8%) · Rank ↓ 7→8 · Conf 67% · momentum → · 91d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 49% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" s="3" t="n">
-        <v>67</v>
+        <v>48.9</v>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
@@ -1696,11 +1778,11 @@
         </is>
       </c>
       <c r="W8" s="3" t="n">
-        <v>53</v>
+        <v>67.2</v>
       </c>
       <c r="X8" s="3" t="inlineStr"/>
       <c r="Y8" s="3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>90</v>
@@ -1708,49 +1790,45 @@
       <c r="AA8" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AB8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
+      <c r="AB8" s="3" t="inlineStr"/>
       <c r="AC8" s="3" t="n">
-        <v>481.4</v>
+        <v>179.92</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>494.35</v>
+        <v>179.92</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>468</v>
+        <v>178.12</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>495</v>
+        <v>181.72</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>457.33</v>
+        <v>170.924</v>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>-7.49</v>
+        <v>-5</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>519.912</v>
+        <v>201.51</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>5.17</v>
+        <v>12</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>556.3058400000001</v>
+        <v>215.6157</v>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>12.53</v>
+        <v>19.84</v>
       </c>
       <c r="AM8" s="3" t="n">
-        <v>482.4</v>
+        <v>186.38</v>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>-0.22</v>
+        <v>-3.47</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>-2.62</v>
+        <v>0</v>
       </c>
       <c r="AP8" s="3" t="n">
         <v>0</v>
@@ -1761,30 +1839,30 @@
       <c r="AR8" s="3" t="inlineStr"/>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT8" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU8" s="3" t="n">
-        <v>5.17</v>
+        <v>12</v>
       </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:47</t>
+          <t>2026-09-02 12:28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>R1-ONGC-IND-20260811-f86a0f</t>
+          <t>R1-VLO-USA-20260902-678f0c</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>ONGC_IND_20260811</t>
+          <t>VLO_USA_20260902</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1794,7 +1872,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1804,7 +1882,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -1816,23 +1894,37 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
-      <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr"/>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.1%) · Rank #9 · Conf 66% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 52% · momentum → · band STRONG · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr"/>
       <c r="U9" s="3" t="n">
-        <v>66</v>
+        <v>51.7</v>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
@@ -1840,11 +1932,11 @@
         </is>
       </c>
       <c r="W9" s="3" t="n">
-        <v>52</v>
+        <v>59.4</v>
       </c>
       <c r="X9" s="3" t="inlineStr"/>
       <c r="Y9" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>90</v>
@@ -1852,79 +1944,79 @@
       <c r="AA9" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AB9" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
+      <c r="AB9" s="3" t="inlineStr"/>
       <c r="AC9" s="3" t="n">
-        <v>236.4</v>
+        <v>361.99</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>239.4499969482422</v>
+        <v>361.99</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>229</v>
+        <v>358.37</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>244</v>
+        <v>365.61</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>224.58</v>
+        <v>343.8905</v>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>-6.21</v>
+        <v>-5</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>255.312</v>
+        <v>405.43</v>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>6.62</v>
+        <v>12</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>273.18384</v>
+        <v>433.8101</v>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>14.09</v>
+        <v>19.84</v>
       </c>
       <c r="AM9" s="3" t="n">
-        <v>233.64</v>
+        <v>358.92</v>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="AP9" s="3" t="inlineStr"/>
-      <c r="AQ9" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AP9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR9" s="3" t="inlineStr"/>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT9" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>6.62</v>
+        <v>12</v>
       </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:47</t>
+          <t>2026-09-02 12:28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>R1-COALINDIA-IND-20260805-292818</t>
+          <t>R1-SNDK-USA-20260902-6a01d7</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA_IND_20260805</t>
+          <t>SNDK_USA_20260902</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1934,7 +2026,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1944,14 +2036,10 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Coal India</t>
-        </is>
-      </c>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -1960,27 +2048,37 @@
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="3" t="inlineStr"/>
-      <c r="O10" s="3" t="inlineStr"/>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.8%) · Rank → 10→10 · Conf 66% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #3 · Conf 43% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr"/>
       <c r="U10" s="3" t="n">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
@@ -1988,11 +2086,11 @@
         </is>
       </c>
       <c r="W10" s="3" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="X10" s="3" t="inlineStr"/>
       <c r="Y10" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>90</v>
@@ -2000,83 +2098,79 @@
       <c r="AA10" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AB10" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
+      <c r="AB10" s="3" t="inlineStr"/>
       <c r="AC10" s="3" t="n">
-        <v>401.6</v>
+        <v>1536.87</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>411.3</v>
+        <v>1536.87</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>390</v>
+        <v>1506.13</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>413</v>
+        <v>1567.61</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>381.52</v>
+        <v>1460.0265</v>
       </c>
       <c r="AH10" s="3" t="n">
-        <v>-7.24</v>
+        <v>-5</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>433.7280000000001</v>
+        <v>1659.8196</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>5.45</v>
+        <v>8</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>464.0889600000001</v>
+        <v>1776.006972</v>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>12.83</v>
+        <v>15.56</v>
       </c>
       <c r="AM10" s="3" t="n">
-        <v>404.2</v>
+        <v>1566.7</v>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>-0.64</v>
+        <v>-1.9</v>
       </c>
       <c r="AO10" s="3" t="n">
-        <v>-2.36</v>
+        <v>0</v>
       </c>
       <c r="AP10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" s="3" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="AR10" s="3" t="inlineStr"/>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT10" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU10" s="3" t="n">
-        <v>5.45</v>
+        <v>8</v>
       </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:47</t>
+          <t>2026-09-02 12:28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>R1-TATASTEEL-IND-20260828-9c799a</t>
+          <t>R1-INCY-USA-20260902-658db3</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>TATASTEEL_IND_20260828</t>
+          <t>INCY_USA_20260902</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2086,7 +2180,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2096,35 +2190,49 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L11" s="3" t="inlineStr"/>
       <c r="M11" s="3" t="inlineStr"/>
-      <c r="N11" s="3" t="inlineStr"/>
-      <c r="O11" s="3" t="inlineStr"/>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.1%) · Rank #11 · Conf 63% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 49% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr"/>
       <c r="U11" s="3" t="n">
-        <v>63</v>
+        <v>48.9</v>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
@@ -2132,11 +2240,11 @@
         </is>
       </c>
       <c r="W11" s="3" t="n">
-        <v>51</v>
+        <v>49.3</v>
       </c>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>90</v>
@@ -2144,79 +2252,79 @@
       <c r="AA11" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AB11" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
+      <c r="AB11" s="3" t="inlineStr"/>
       <c r="AC11" s="3" t="n">
-        <v>184.1</v>
+        <v>125.01</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>187.4600067138672</v>
+        <v>125.01</v>
       </c>
       <c r="AE11" s="3" t="n">
-        <v>178</v>
+        <v>122.51</v>
       </c>
       <c r="AF11" s="3" t="n">
-        <v>190</v>
+        <v>127.51</v>
       </c>
       <c r="AG11" s="3" t="n">
-        <v>174.895</v>
+        <v>118.7595</v>
       </c>
       <c r="AH11" s="3" t="n">
-        <v>-6.7</v>
+        <v>-5</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>198.828</v>
+        <v>135.0108</v>
       </c>
       <c r="AJ11" s="3" t="n">
-        <v>6.06</v>
+        <v>8</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>212.74596</v>
+        <v>144.461556</v>
       </c>
       <c r="AL11" s="3" t="n">
-        <v>13.49</v>
+        <v>15.56</v>
       </c>
       <c r="AM11" s="3" t="n">
-        <v>182.3</v>
+        <v>123.22</v>
       </c>
       <c r="AN11" s="3" t="n">
-        <v>0.97</v>
+        <v>1.45</v>
       </c>
       <c r="AO11" s="3" t="n">
-        <v>-1.79</v>
-      </c>
-      <c r="AP11" s="3" t="inlineStr"/>
-      <c r="AQ11" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AP11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR11" s="3" t="inlineStr"/>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT11" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU11" s="3" t="n">
-        <v>6.06</v>
+        <v>8</v>
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:47</t>
+          <t>2026-09-02 12:28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>R2-CHAMBLFERT-IND-20260804-5eb424</t>
+          <t>R1-GRMN-USA-20260902-dc608d</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CHAMBLFERT_IND_20260804</t>
+          <t>GRMN_USA_20260902</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2226,24 +2334,20 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Chambal Fert.</t>
-        </is>
-      </c>
+          <t>GRMN</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
       <c r="H12" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2252,27 +2356,37 @@
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M12" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="N12" s="3" t="inlineStr"/>
-      <c r="O12" s="3" t="inlineStr"/>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 3→8 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 49% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr"/>
       <c r="U12" s="3" t="n">
-        <v>38.3</v>
+        <v>48.9</v>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
@@ -2280,89 +2394,91 @@
         </is>
       </c>
       <c r="W12" s="3" t="n">
-        <v>22.4</v>
+        <v>48.7</v>
       </c>
       <c r="X12" s="3" t="inlineStr"/>
       <c r="Y12" s="3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA12" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB12" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB12" s="3" t="inlineStr"/>
       <c r="AC12" s="3" t="n">
-        <v>443.35</v>
+        <v>275.17</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>443.35</v>
+        <v>275.17</v>
       </c>
       <c r="AE12" s="3" t="n">
-        <v>438.92</v>
+        <v>269.67</v>
       </c>
       <c r="AF12" s="3" t="n">
-        <v>447.78</v>
+        <v>280.67</v>
       </c>
       <c r="AG12" s="3" t="n">
-        <v>421.1825</v>
+        <v>261.4115</v>
       </c>
       <c r="AH12" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>478.818</v>
+        <v>297.1836</v>
       </c>
       <c r="AJ12" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>509.8525</v>
+        <v>317.986452</v>
       </c>
       <c r="AL12" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM12" s="3" t="n">
-        <v>413.55</v>
+        <v>284.11</v>
       </c>
       <c r="AN12" s="3" t="n">
-        <v>-0.3</v>
+        <v>-3.15</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP12" s="3" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AQ12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AR12" s="3" t="inlineStr"/>
-      <c r="AS12" s="3" t="inlineStr"/>
-      <c r="AT12" s="3" t="inlineStr"/>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU12" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:47</t>
+          <t>2026-09-02 12:28</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>R2-PNB-IND-20260804-c7957c</t>
+          <t>R1-MU-USA-20260902-2ba5dc</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>PNB_IND_20260804</t>
+          <t>MU_USA_20260902</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2372,24 +2488,20 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Punjab Natl. Bank</t>
-        </is>
-      </c>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2398,27 +2510,37 @@
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="3" t="inlineStr"/>
-      <c r="O13" s="3" t="inlineStr"/>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="3" t="inlineStr"/>
-      <c r="R13" s="3" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 32% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #6 · Conf 49% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr"/>
       <c r="U13" s="3" t="n">
-        <v>32.1</v>
+        <v>48.9</v>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
@@ -2426,58 +2548,54 @@
         </is>
       </c>
       <c r="W13" s="3" t="n">
-        <v>22.2</v>
+        <v>48.5</v>
       </c>
       <c r="X13" s="3" t="inlineStr"/>
       <c r="Y13" s="3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA13" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB13" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB13" s="3" t="inlineStr"/>
       <c r="AC13" s="3" t="n">
-        <v>113.36</v>
+        <v>933.4400000000001</v>
       </c>
       <c r="AD13" s="3" t="n">
-        <v>113.36</v>
+        <v>933.4400000000001</v>
       </c>
       <c r="AE13" s="3" t="n">
-        <v>112.23</v>
+        <v>924.11</v>
       </c>
       <c r="AF13" s="3" t="n">
-        <v>114.49</v>
+        <v>942.77</v>
       </c>
       <c r="AG13" s="3" t="n">
-        <v>107.692</v>
+        <v>886.768</v>
       </c>
       <c r="AH13" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>122.4288</v>
+        <v>1045.45</v>
       </c>
       <c r="AJ13" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>130.364</v>
+        <v>1118.6315</v>
       </c>
       <c r="AL13" s="3" t="n">
-        <v>15</v>
+        <v>19.84</v>
       </c>
       <c r="AM13" s="3" t="n">
-        <v>113.33</v>
+        <v>958.73</v>
       </c>
       <c r="AN13" s="3" t="n">
-        <v>1.67</v>
+        <v>-2.64</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>0</v>
@@ -2486,29 +2604,35 @@
         <v>0</v>
       </c>
       <c r="AQ13" s="3" t="n">
-        <v>-2.01</v>
+        <v>0</v>
       </c>
       <c r="AR13" s="3" t="inlineStr"/>
-      <c r="AS13" s="3" t="inlineStr"/>
-      <c r="AT13" s="3" t="inlineStr"/>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU13" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:47</t>
+          <t>2026-09-02 12:28</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>R2-ITC-IND-20260804-a049df</t>
+          <t>R1-MSFT-USA-20260902-880456</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ITC_IND_20260804</t>
+          <t>MSFT_USA_20260902</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2518,22 +2642,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -2544,27 +2668,37 @@
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L14" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="M14" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N14" s="3" t="inlineStr"/>
-      <c r="O14" s="3" t="inlineStr"/>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 7→9 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 52% · momentum → · band HOLD→STRONG · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="n">
-        <v>38.3</v>
+        <v>51.7</v>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
@@ -2572,89 +2706,91 @@
         </is>
       </c>
       <c r="W14" s="3" t="n">
-        <v>21.6</v>
+        <v>48</v>
       </c>
       <c r="X14" s="3" t="inlineStr"/>
       <c r="Y14" s="3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA14" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB14" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB14" s="3" t="inlineStr"/>
       <c r="AC14" s="3" t="n">
-        <v>282.9</v>
+        <v>501.02</v>
       </c>
       <c r="AD14" s="3" t="n">
-        <v>282.9</v>
+        <v>501.02</v>
       </c>
       <c r="AE14" s="3" t="n">
-        <v>280.07</v>
+        <v>491</v>
       </c>
       <c r="AF14" s="3" t="n">
-        <v>285.73</v>
+        <v>511.04</v>
       </c>
       <c r="AG14" s="3" t="n">
-        <v>268.7549999999999</v>
+        <v>475.9689999999999</v>
       </c>
       <c r="AH14" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>305.532</v>
+        <v>541.1016</v>
       </c>
       <c r="AJ14" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>325.3349999999999</v>
+        <v>578.978712</v>
       </c>
       <c r="AL14" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM14" s="3" t="n">
-        <v>264.9</v>
+        <v>507.29</v>
       </c>
       <c r="AN14" s="3" t="n">
-        <v>0.64</v>
+        <v>-1.24</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP14" s="3" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AQ14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AR14" s="3" t="inlineStr"/>
-      <c r="AS14" s="3" t="inlineStr"/>
-      <c r="AT14" s="3" t="inlineStr"/>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU14" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:47</t>
+          <t>2026-09-02 12:28</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>R2-BATAINDIA-IND-20260804-21b729</t>
+          <t>R1-HON-USA-20260902-c15300</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>BATAINDIA_IND_20260804</t>
+          <t>HON_USA_20260902</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2664,22 +2800,22 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Bata India</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -2690,27 +2826,37 @@
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr"/>
       <c r="K15" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
-      <c r="O15" s="3" t="inlineStr"/>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 15→15 · Conf 24% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr"/>
       <c r="U15" s="3" t="n">
-        <v>24</v>
+        <v>54.5</v>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
@@ -2718,58 +2864,54 @@
         </is>
       </c>
       <c r="W15" s="3" t="n">
-        <v>-30.3</v>
+        <v>47.4</v>
       </c>
       <c r="X15" s="3" t="inlineStr"/>
       <c r="Y15" s="3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA15" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB15" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB15" s="3" t="inlineStr"/>
       <c r="AC15" s="3" t="n">
-        <v>709</v>
+        <v>209.98</v>
       </c>
       <c r="AD15" s="3" t="n">
-        <v>709</v>
+        <v>209.98</v>
       </c>
       <c r="AE15" s="3" t="n">
-        <v>701.91</v>
+        <v>205.78</v>
       </c>
       <c r="AF15" s="3" t="n">
-        <v>716.09</v>
+        <v>214.18</v>
       </c>
       <c r="AG15" s="3" t="n">
-        <v>673.55</v>
+        <v>199.481</v>
       </c>
       <c r="AH15" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>765.72</v>
+        <v>226.7784</v>
       </c>
       <c r="AJ15" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>815.3499999999999</v>
+        <v>242.652888</v>
       </c>
       <c r="AL15" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM15" s="3" t="n">
-        <v>676.2</v>
+        <v>213.53</v>
       </c>
       <c r="AN15" s="3" t="n">
-        <v>0.17</v>
+        <v>-1.66</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>0</v>
@@ -2778,29 +2920,35 @@
         <v>0</v>
       </c>
       <c r="AQ15" s="3" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="AR15" s="3" t="inlineStr"/>
-      <c r="AS15" s="3" t="inlineStr"/>
-      <c r="AT15" s="3" t="inlineStr"/>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU15" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:47</t>
+          <t>2026-09-02 12:28</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>R2-PERSISTENT-IND-20260805-48a8e2</t>
+          <t>R1-EXPD-USA-20260902-056a7c</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>PERSISTENT_IND_20260805</t>
+          <t>EXPD_USA_20260902</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2810,17 +2958,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr"/>
@@ -2832,27 +2980,37 @@
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="3" t="inlineStr"/>
-      <c r="O16" s="3" t="inlineStr"/>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 41% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 49% · momentum → · band STRONG · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr"/>
       <c r="U16" s="3" t="n">
-        <v>40.7</v>
+        <v>48.9</v>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
@@ -2860,89 +3018,91 @@
         </is>
       </c>
       <c r="W16" s="3" t="n">
-        <v>23.8</v>
+        <v>42.6</v>
       </c>
       <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA16" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB16" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB16" s="3" t="inlineStr"/>
       <c r="AC16" s="3" t="n">
-        <v>5322.4</v>
+        <v>187.7</v>
       </c>
       <c r="AD16" s="3" t="n">
-        <v>5322.4</v>
+        <v>187.7</v>
       </c>
       <c r="AE16" s="3" t="n">
-        <v>5269.18</v>
+        <v>183.95</v>
       </c>
       <c r="AF16" s="3" t="n">
-        <v>5375.62</v>
+        <v>191.45</v>
       </c>
       <c r="AG16" s="3" t="n">
-        <v>5056.28</v>
+        <v>178.315</v>
       </c>
       <c r="AH16" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>5748.192</v>
+        <v>202.716</v>
       </c>
       <c r="AJ16" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>6120.759999999999</v>
+        <v>216.90612</v>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM16" s="3" t="n">
-        <v>5625.5</v>
+        <v>189.65</v>
       </c>
       <c r="AN16" s="3" t="n">
-        <v>3.1</v>
+        <v>-1.03</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP16" s="3" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AQ16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AR16" s="3" t="inlineStr"/>
-      <c r="AS16" s="3" t="inlineStr"/>
-      <c r="AT16" s="3" t="inlineStr"/>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU16" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:47</t>
+          <t>2026-09-02 12:28</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>R2-BAJAJHLDNG-IND-20260805-660791</t>
+          <t>R1-OXY-USA-20260902-67e560</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG_IND_20260805</t>
+          <t>OXY_USA_20260902</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2952,17 +3112,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
@@ -2976,25 +3136,35 @@
       <c r="K17" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L17" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr"/>
-      <c r="P17" s="3" t="inlineStr"/>
-      <c r="Q17" s="3" t="inlineStr"/>
-      <c r="R17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 52% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr"/>
       <c r="U17" s="3" t="n">
-        <v>38.3</v>
+        <v>51.7</v>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
@@ -3002,89 +3172,91 @@
         </is>
       </c>
       <c r="W17" s="3" t="n">
-        <v>20.7</v>
+        <v>40.6</v>
       </c>
       <c r="X17" s="3" t="inlineStr"/>
       <c r="Y17" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA17" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB17" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB17" s="3" t="inlineStr"/>
       <c r="AC17" s="3" t="n">
-        <v>11127</v>
+        <v>60.95</v>
       </c>
       <c r="AD17" s="3" t="n">
-        <v>11127</v>
+        <v>60.95</v>
       </c>
       <c r="AE17" s="3" t="n">
-        <v>11015.73</v>
+        <v>59.73</v>
       </c>
       <c r="AF17" s="3" t="n">
-        <v>11238.27</v>
+        <v>62.17</v>
       </c>
       <c r="AG17" s="3" t="n">
-        <v>10570.65</v>
+        <v>57.9025</v>
       </c>
       <c r="AH17" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>12017.16</v>
+        <v>65.82600000000001</v>
       </c>
       <c r="AJ17" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>12796.05</v>
+        <v>70.43382000000001</v>
       </c>
       <c r="AL17" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM17" s="3" t="n">
-        <v>11333</v>
+        <v>60.18</v>
       </c>
       <c r="AN17" s="3" t="n">
-        <v>-0.2</v>
+        <v>1.28</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP17" s="3" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="AQ17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AR17" s="3" t="inlineStr"/>
-      <c r="AS17" s="3" t="inlineStr"/>
-      <c r="AT17" s="3" t="inlineStr"/>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU17" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:47</t>
+          <t>2026-09-02 12:28</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>R2-LICI-IND-20260805-a4f409</t>
+          <t>R2-TRV-USA-20260810-a2c57b</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>LICI_IND_20260805</t>
+          <t>TRV_USA_20260810</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -3094,7 +3266,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3104,10 +3276,14 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>LICI</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -3116,10 +3292,14 @@
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L18" s="3" t="inlineStr"/>
-      <c r="M18" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="N18" s="3" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr"/>
       <c r="P18" s="3" t="inlineStr"/>
@@ -3127,12 +3307,12 @@
       <c r="R18" s="3" t="inlineStr"/>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #9 · Conf 37% · momentum → · 61d left · → HOLD</t>
+          <t>Rank → 1→1 · Conf 57% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr"/>
       <c r="U18" s="3" t="n">
-        <v>37.2</v>
+        <v>56.8</v>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
@@ -3140,11 +3320,11 @@
         </is>
       </c>
       <c r="W18" s="3" t="n">
-        <v>20.6</v>
+        <v>29.2</v>
       </c>
       <c r="X18" s="3" t="inlineStr"/>
       <c r="Y18" s="3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>60</v>
@@ -3154,75 +3334,47 @@
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="AC18" s="3" t="n">
-        <v>391.3</v>
-      </c>
-      <c r="AD18" s="3" t="n">
-        <v>391.3</v>
-      </c>
-      <c r="AE18" s="3" t="n">
-        <v>387.39</v>
-      </c>
-      <c r="AF18" s="3" t="n">
-        <v>395.21</v>
-      </c>
-      <c r="AG18" s="3" t="n">
-        <v>371.735</v>
-      </c>
-      <c r="AH18" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI18" s="3" t="n">
-        <v>422.604</v>
-      </c>
-      <c r="AJ18" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK18" s="3" t="n">
-        <v>449.995</v>
-      </c>
-      <c r="AL18" s="3" t="n">
-        <v>15</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr"/>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr"/>
+      <c r="AF18" s="3" t="inlineStr"/>
+      <c r="AG18" s="3" t="inlineStr"/>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr"/>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr"/>
       <c r="AM18" s="3" t="n">
-        <v>413.95</v>
+        <v>365.93</v>
       </c>
       <c r="AN18" s="3" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="AO18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.55</v>
+      </c>
+      <c r="AO18" s="3" t="inlineStr"/>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr"/>
       <c r="AS18" s="3" t="inlineStr"/>
       <c r="AT18" s="3" t="inlineStr"/>
-      <c r="AU18" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AU18" s="3" t="inlineStr"/>
       <c r="AV18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:47</t>
+          <t>2026-09-02 12:28</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>R2-TIINDIA-IND-20260805-44fbae</t>
+          <t>R2-V-USA-20260810-1697f4</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA_IND_20260805</t>
+          <t>V_USA_20260810</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3232,7 +3384,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -3242,10 +3394,14 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr"/>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -3254,10 +3410,14 @@
       <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="N19" s="3" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr"/>
       <c r="P19" s="3" t="inlineStr"/>
@@ -3265,12 +3425,12 @@
       <c r="R19" s="3" t="inlineStr"/>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #12 · Conf 22% · momentum → · 61d left · → HOLD</t>
+          <t>Rank → 2→2 · Conf 54% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr"/>
       <c r="U19" s="3" t="n">
-        <v>21.5</v>
+        <v>53.6</v>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
@@ -3278,11 +3438,11 @@
         </is>
       </c>
       <c r="W19" s="3" t="n">
-        <v>-25.9</v>
+        <v>27.8</v>
       </c>
       <c r="X19" s="3" t="inlineStr"/>
       <c r="Y19" s="3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>60</v>
@@ -3292,958 +3452,40 @@
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="AC19" s="3" t="n">
-        <v>2744.3</v>
-      </c>
-      <c r="AD19" s="3" t="n">
-        <v>2744.3</v>
-      </c>
-      <c r="AE19" s="3" t="n">
-        <v>2716.86</v>
-      </c>
-      <c r="AF19" s="3" t="n">
-        <v>2771.74</v>
-      </c>
-      <c r="AG19" s="3" t="n">
-        <v>2607.085</v>
-      </c>
-      <c r="AH19" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI19" s="3" t="n">
-        <v>2963.844000000001</v>
-      </c>
-      <c r="AJ19" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK19" s="3" t="n">
-        <v>3155.945</v>
-      </c>
-      <c r="AL19" s="3" t="n">
-        <v>15</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr"/>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr"/>
+      <c r="AF19" s="3" t="inlineStr"/>
+      <c r="AG19" s="3" t="inlineStr"/>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr"/>
       <c r="AM19" s="3" t="n">
-        <v>2775.9</v>
+        <v>379.37</v>
       </c>
       <c r="AN19" s="3" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="AO19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-1.77</v>
+      </c>
+      <c r="AO19" s="3" t="inlineStr"/>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr"/>
       <c r="AS19" s="3" t="inlineStr"/>
       <c r="AT19" s="3" t="inlineStr"/>
-      <c r="AU19" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AU19" s="3" t="inlineStr"/>
       <c r="AV19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>R1-ICICIBANK-IND-20260804-bfcaee</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>ICICIBANK_IND_20260804</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>ICICIBANK</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>ICICI Bank</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3" t="inlineStr"/>
-      <c r="O20" s="3" t="inlineStr"/>
-      <c r="P20" s="3" t="inlineStr"/>
-      <c r="Q20" s="3" t="inlineStr"/>
-      <c r="R20" s="3" t="inlineStr"/>
-      <c r="S20" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 2→2 · Conf 83% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T20" s="3" t="inlineStr"/>
-      <c r="U20" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="V20" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="X20" s="3" t="inlineStr"/>
-      <c r="Y20" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z20" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA20" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB20" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC20" s="3" t="n">
-        <v>1438.5</v>
-      </c>
-      <c r="AD20" s="3" t="n">
-        <v>1438.5</v>
-      </c>
-      <c r="AE20" s="3" t="n">
-        <v>1424.12</v>
-      </c>
-      <c r="AF20" s="3" t="n">
-        <v>1452.88</v>
-      </c>
-      <c r="AG20" s="3" t="n">
-        <v>1366.575</v>
-      </c>
-      <c r="AH20" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI20" s="3" t="n">
-        <v>1553.58</v>
-      </c>
-      <c r="AJ20" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK20" s="3" t="n">
-        <v>1654.275</v>
-      </c>
-      <c r="AL20" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM20" s="3" t="n">
-        <v>1432</v>
-      </c>
-      <c r="AN20" s="3" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AO20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" s="3" t="inlineStr"/>
-      <c r="AS20" s="3" t="inlineStr"/>
-      <c r="AT20" s="3" t="inlineStr"/>
-      <c r="AU20" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV20" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>R1-LUPIN-IND-20260805-6a4927</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>LUPIN_IND_20260805</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>LUPIN</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Lupin</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
-        </is>
-      </c>
-      <c r="S21" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-11.5%) · Rank → 3→3 · Conf 72% · momentum → · band HOLD · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T21" s="3" t="inlineStr">
-        <is>
-          <t>CRITICAL·DEEP_LOSS·-10.6% ≤ -8.0% · EXIT URGENT</t>
-        </is>
-      </c>
-      <c r="U21" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="V21" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="X21" s="3" t="inlineStr"/>
-      <c r="Y21" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z21" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA21" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB21" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="AC21" s="3" t="n">
-        <v>2160.2</v>
-      </c>
-      <c r="AD21" s="3" t="n">
-        <v>2417</v>
-      </c>
-      <c r="AE21" s="3" t="n">
-        <v>2392.83</v>
-      </c>
-      <c r="AF21" s="3" t="n">
-        <v>2441.17</v>
-      </c>
-      <c r="AG21" s="3" t="n">
-        <v>2296.15</v>
-      </c>
-      <c r="AH21" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI21" s="3" t="n">
-        <v>2610.36</v>
-      </c>
-      <c r="AJ21" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK21" s="3" t="n">
-        <v>2779.55</v>
-      </c>
-      <c r="AL21" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM21" s="3" t="n">
-        <v>2159.6</v>
-      </c>
-      <c r="AN21" s="3" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AO21" s="3" t="n">
-        <v>-10.62</v>
-      </c>
-      <c r="AP21" s="3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ21" s="3" t="n">
-        <v>-10.62</v>
-      </c>
-      <c r="AR21" s="3" t="inlineStr"/>
-      <c r="AS21" s="3" t="inlineStr"/>
-      <c r="AT21" s="3" t="inlineStr"/>
-      <c r="AU21" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>R1-PIDILITIND-IND-20260804-c2e1ef</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>PIDILITIND_IND_20260804</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>PIDILITIND</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Pidilite</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr"/>
-      <c r="J22" s="3" t="inlineStr"/>
-      <c r="K22" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3" t="inlineStr"/>
-      <c r="O22" s="3" t="inlineStr"/>
-      <c r="P22" s="3" t="inlineStr"/>
-      <c r="Q22" s="3" t="inlineStr"/>
-      <c r="R22" s="3" t="inlineStr"/>
-      <c r="S22" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 3→3 · Conf 87% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T22" s="3" t="inlineStr"/>
-      <c r="U22" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="V22" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W22" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="X22" s="3" t="inlineStr"/>
-      <c r="Y22" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z22" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA22" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB22" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC22" s="3" t="n">
-        <v>1625.5</v>
-      </c>
-      <c r="AD22" s="3" t="n">
-        <v>1625.5</v>
-      </c>
-      <c r="AE22" s="3" t="n">
-        <v>1609.24</v>
-      </c>
-      <c r="AF22" s="3" t="n">
-        <v>1641.76</v>
-      </c>
-      <c r="AG22" s="3" t="n">
-        <v>1544.225</v>
-      </c>
-      <c r="AH22" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI22" s="3" t="n">
-        <v>1755.54</v>
-      </c>
-      <c r="AJ22" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK22" s="3" t="n">
-        <v>1869.325</v>
-      </c>
-      <c r="AL22" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM22" s="3" t="n">
-        <v>1617.2</v>
-      </c>
-      <c r="AN22" s="3" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AO22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" s="3" t="inlineStr"/>
-      <c r="AS22" s="3" t="inlineStr"/>
-      <c r="AT22" s="3" t="inlineStr"/>
-      <c r="AU22" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>R1-KOTAKBANK-IND-20260804-5087ff</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>KOTAKBANK_IND_20260804</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Kotak Bank</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr"/>
-      <c r="J23" s="3" t="inlineStr"/>
-      <c r="K23" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="3" t="inlineStr"/>
-      <c r="O23" s="3" t="inlineStr"/>
-      <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="3" t="inlineStr"/>
-      <c r="R23" s="3" t="inlineStr"/>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 5→5 · Conf 71% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T23" s="3" t="inlineStr"/>
-      <c r="U23" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="V23" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W23" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="X23" s="3" t="inlineStr"/>
-      <c r="Y23" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z23" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA23" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB23" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC23" s="3" t="n">
-        <v>389.3</v>
-      </c>
-      <c r="AD23" s="3" t="n">
-        <v>389.3</v>
-      </c>
-      <c r="AE23" s="3" t="n">
-        <v>385.41</v>
-      </c>
-      <c r="AF23" s="3" t="n">
-        <v>393.19</v>
-      </c>
-      <c r="AG23" s="3" t="n">
-        <v>369.835</v>
-      </c>
-      <c r="AH23" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI23" s="3" t="n">
-        <v>420.444</v>
-      </c>
-      <c r="AJ23" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK23" s="3" t="n">
-        <v>447.695</v>
-      </c>
-      <c r="AL23" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM23" s="3" t="n">
-        <v>422.8</v>
-      </c>
-      <c r="AN23" s="3" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="AO23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" s="3" t="inlineStr"/>
-      <c r="AS23" s="3" t="inlineStr"/>
-      <c r="AT23" s="3" t="inlineStr"/>
-      <c r="AU23" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>R1-BRITANNIA-IND-20260804-1de7ba</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>BRITANNIA_IND_20260804</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr"/>
-      <c r="J24" s="3" t="inlineStr"/>
-      <c r="K24" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3" t="inlineStr"/>
-      <c r="O24" s="3" t="inlineStr"/>
-      <c r="P24" s="3" t="inlineStr"/>
-      <c r="Q24" s="3" t="inlineStr"/>
-      <c r="R24" s="3" t="inlineStr"/>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 9→9 · Conf 66% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T24" s="3" t="inlineStr"/>
-      <c r="U24" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="V24" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="X24" s="3" t="inlineStr"/>
-      <c r="Y24" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z24" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA24" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB24" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC24" s="3" t="n">
-        <v>5406</v>
-      </c>
-      <c r="AD24" s="3" t="n">
-        <v>5406</v>
-      </c>
-      <c r="AE24" s="3" t="n">
-        <v>5351.94</v>
-      </c>
-      <c r="AF24" s="3" t="n">
-        <v>5460.06</v>
-      </c>
-      <c r="AG24" s="3" t="n">
-        <v>5135.7</v>
-      </c>
-      <c r="AH24" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI24" s="3" t="n">
-        <v>5838.48</v>
-      </c>
-      <c r="AJ24" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK24" s="3" t="n">
-        <v>6216.9</v>
-      </c>
-      <c r="AL24" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM24" s="3" t="n">
-        <v>5323</v>
-      </c>
-      <c r="AN24" s="3" t="n">
-        <v>-1.28</v>
-      </c>
-      <c r="AO24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" s="3" t="inlineStr"/>
-      <c r="AS24" s="3" t="inlineStr"/>
-      <c r="AT24" s="3" t="inlineStr"/>
-      <c r="AU24" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV24" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>R1-TATAPOWER-IND-20260804-dafbb4</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>TATAPOWER_IND_20260804</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>TATAPOWER</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Tata Power</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="3" t="inlineStr"/>
-      <c r="K25" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr"/>
-      <c r="O25" s="3" t="inlineStr"/>
-      <c r="P25" s="3" t="inlineStr"/>
-      <c r="Q25" s="3" t="inlineStr"/>
-      <c r="R25" s="3" t="inlineStr"/>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 6→6 · Conf 64% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="inlineStr"/>
-      <c r="U25" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="X25" s="3" t="inlineStr"/>
-      <c r="Y25" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z25" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA25" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB25" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC25" s="3" t="n">
-        <v>381.6</v>
-      </c>
-      <c r="AD25" s="3" t="n">
-        <v>381.6</v>
-      </c>
-      <c r="AE25" s="3" t="n">
-        <v>377.78</v>
-      </c>
-      <c r="AF25" s="3" t="n">
-        <v>385.42</v>
-      </c>
-      <c r="AG25" s="3" t="n">
-        <v>362.52</v>
-      </c>
-      <c r="AH25" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI25" s="3" t="n">
-        <v>412.128</v>
-      </c>
-      <c r="AJ25" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK25" s="3" t="n">
-        <v>438.84</v>
-      </c>
-      <c r="AL25" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM25" s="3" t="n">
-        <v>348.55</v>
-      </c>
-      <c r="AN25" s="3" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AO25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" s="3" t="inlineStr"/>
-      <c r="AS25" s="3" t="inlineStr"/>
-      <c r="AT25" s="3" t="inlineStr"/>
-      <c r="AU25" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV25" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:47</t>
+          <t>2026-09-02 12:28</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV25"/>
+  <autoFilter ref="A1:AV19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_daily_2026-09-02.xlsx
+++ b/reports/telegram/aegis_daily_2026-09-02.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV19"/>
+  <dimension ref="A1:AV14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -886,19 +886,19 @@
       </c>
       <c r="AV2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 12:28</t>
+          <t>2026-09-02 13:42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>R2-INCY-USA-20260902-924c1b</t>
+          <t>R1-PLTR-USA-20260902-1a2a27</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>INCY_USA_20260902</t>
+          <t>PLTR_USA_20260902</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -913,35 +913,29 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>→ PLTR · +12.5pp alpha</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
@@ -961,7 +955,7 @@
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank #4 · Conf 49% · band HOLD · 60d left · → EXIT (rotate to PLTR)</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 49% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr"/>
@@ -974,93 +968,91 @@
         </is>
       </c>
       <c r="W3" s="3" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="X3" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>67.2</v>
+      </c>
+      <c r="X3" s="3" t="inlineStr"/>
       <c r="Y3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA3" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB3" s="3" t="inlineStr"/>
       <c r="AC3" s="3" t="n">
-        <v>125.01</v>
+        <v>179.92</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>125.01</v>
+        <v>179.92</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>123.76</v>
+        <v>178.12</v>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>126.26</v>
+        <v>181.72</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>118.76</v>
+        <v>170.924</v>
       </c>
       <c r="AH3" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>135.01</v>
+        <v>201.51</v>
       </c>
       <c r="AJ3" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>143.76</v>
+        <v>215.6157</v>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>15</v>
+        <v>19.84</v>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>123.22</v>
+        <v>186.38</v>
       </c>
       <c r="AN3" s="3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO3" s="3" t="inlineStr"/>
+        <v>-3.47</v>
+      </c>
+      <c r="AO3" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AP3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR3" s="3" t="inlineStr">
-        <is>
-          <t>Quality · Event Driven · Momentum</t>
-        </is>
-      </c>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr"/>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU3" s="3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 12:28</t>
+          <t>2026-09-02 13:42</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>R2-OXY-USA-20260902-bcdb9b</t>
+          <t>R1-VLO-USA-20260902-678f0c</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>OXY_USA_20260902</t>
+          <t>VLO_USA_20260902</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1075,35 +1067,29 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>→ PLTR · +13.9pp alpha</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="3" t="n">
-        <v>78.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
@@ -1123,7 +1109,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank #8 · Conf 52% · band HOLD · 60d left · → EXIT (rotate to PLTR)</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 52% · momentum → · band STRONG · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr"/>
@@ -1136,88 +1122,86 @@
         </is>
       </c>
       <c r="W4" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="X4" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>59.4</v>
+      </c>
+      <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA4" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB4" s="3" t="inlineStr"/>
       <c r="AC4" s="3" t="n">
-        <v>60.95</v>
+        <v>361.99</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>60.95</v>
+        <v>361.99</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>60.34</v>
+        <v>358.37</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>61.56</v>
+        <v>365.61</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>57.9</v>
+        <v>343.8905</v>
       </c>
       <c r="AH4" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>65.83</v>
+        <v>405.43</v>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>8.01</v>
+        <v>12</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>70.09</v>
+        <v>433.8101</v>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>15</v>
+        <v>19.84</v>
       </c>
       <c r="AM4" s="3" t="n">
-        <v>60.18</v>
+        <v>358.92</v>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AO4" s="3" t="inlineStr"/>
+        <v>0.86</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AP4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR4" s="3" t="inlineStr">
-        <is>
-          <t>Value · Momentum · Event Driven</t>
-        </is>
-      </c>
-      <c r="AS4" s="3" t="inlineStr"/>
-      <c r="AT4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr"/>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU4" s="3" t="n">
-        <v>13.89</v>
+        <v>12</v>
       </c>
       <c r="AV4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 12:28</t>
+          <t>2026-09-02 13:42</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>R2-SNDK-USA-20260902-3414ff</t>
+          <t>R1-SNDK-USA-20260902-6a01d7</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1237,7 +1221,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1248,19 +1232,13 @@
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>→ PLTR · +14.2pp alpha</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
@@ -1285,7 +1263,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank #10 · Conf 43% · band HOLD · 60d left · → EXIT (rotate to PLTR)</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #3 · Conf 43% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr"/>
@@ -1298,25 +1276,19 @@
         </is>
       </c>
       <c r="W5" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="X5" s="3" t="inlineStr"/>
       <c r="Y5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA5" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB5" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB5" s="3" t="inlineStr"/>
       <c r="AC5" s="3" t="n">
         <v>1536.87</v>
       </c>
@@ -1324,28 +1296,28 @@
         <v>1536.87</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>1521.5</v>
+        <v>1506.13</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>1552.24</v>
+        <v>1567.61</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>1460.03</v>
+        <v>1460.0265</v>
       </c>
       <c r="AH5" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>1659.82</v>
+        <v>1659.8196</v>
       </c>
       <c r="AJ5" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>1767.4</v>
+        <v>1776.006972</v>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM5" s="3" t="n">
         <v>1566.7</v>
@@ -1353,38 +1325,42 @@
       <c r="AN5" s="3" t="n">
         <v>-1.9</v>
       </c>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AP5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR5" s="3" t="inlineStr">
-        <is>
-          <t>Quality · Mean Reversion · Growth</t>
-        </is>
-      </c>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr"/>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU5" s="3" t="n">
-        <v>14.2</v>
+        <v>8</v>
       </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 12:28</t>
+          <t>2026-09-02 13:42</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>R2-XYZ-USA-20260902-cea5af</t>
+          <t>R1-INCY-USA-20260902-658db3</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>XYZ_USA_20260902</t>
+          <t>INCY_USA_20260902</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1399,43 +1375,37 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>→ PLTR · +66.0pp alpha</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="3" t="n">
-        <v>52.5</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>🔴</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
-        <v>29.1</v>
+        <v>48.2</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>-0.8</v>
@@ -1447,12 +1417,12 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank #11 · Conf 30% · band EXIT · 60d left · → EXIT (rotate to PLTR)</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 49% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" s="3" t="n">
-        <v>29.9</v>
+        <v>48.9</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
@@ -1460,93 +1430,91 @@
         </is>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-26.5</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>49.3</v>
+      </c>
+      <c r="X6" s="3" t="inlineStr"/>
       <c r="Y6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA6" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB6" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB6" s="3" t="inlineStr"/>
       <c r="AC6" s="3" t="n">
-        <v>77.88</v>
+        <v>125.01</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>77.88</v>
+        <v>125.01</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>122.51</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>78.66</v>
+        <v>127.51</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>73.98999999999999</v>
+        <v>118.7595</v>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>-4.99</v>
+        <v>-5</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>84.11</v>
+        <v>135.0108</v>
       </c>
       <c r="AJ6" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>89.56</v>
+        <v>144.461556</v>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM6" s="3" t="n">
-        <v>82.02</v>
+        <v>123.22</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>-5.05</v>
-      </c>
-      <c r="AO6" s="3" t="inlineStr"/>
+        <v>1.45</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AP6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR6" s="3" t="inlineStr">
-        <is>
-          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
-        </is>
-      </c>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU6" s="3" t="n">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 12:28</t>
+          <t>2026-09-02 13:42</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>R2-SW-USA-20260902-015fe2</t>
+          <t>R1-GRMN-USA-20260902-dc608d</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SW_USA_20260902</t>
+          <t>GRMN_USA_20260902</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1561,43 +1529,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>→ PLTR · +75.9pp alpha</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="n">
-        <v>52.4</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>🔴</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>27.1</v>
+        <v>48.1</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>-0.8</v>
@@ -1609,12 +1571,12 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank #15 · Conf 28% · band EXIT · 60d left · → EXIT (rotate to PLTR)</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 49% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="n">
-        <v>27.8</v>
+        <v>48.9</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -1622,93 +1584,91 @@
         </is>
       </c>
       <c r="W7" s="3" t="n">
-        <v>-36.4</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>48.7</v>
+      </c>
+      <c r="X7" s="3" t="inlineStr"/>
       <c r="Y7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA7" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB7" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB7" s="3" t="inlineStr"/>
       <c r="AC7" s="3" t="n">
-        <v>45.43</v>
+        <v>275.17</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>45.43</v>
+        <v>275.17</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>44.98</v>
+        <v>269.67</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>45.88</v>
+        <v>280.67</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>43.16</v>
+        <v>261.4115</v>
       </c>
       <c r="AH7" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>49.06</v>
+        <v>297.1836</v>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>7.99</v>
+        <v>8</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>52.24</v>
+        <v>317.986452</v>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>14.99</v>
+        <v>15.56</v>
       </c>
       <c r="AM7" s="3" t="n">
-        <v>46.9</v>
+        <v>284.11</v>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>-3.13</v>
-      </c>
-      <c r="AO7" s="3" t="inlineStr"/>
+        <v>-3.15</v>
+      </c>
+      <c r="AO7" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AP7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR7" s="3" t="inlineStr">
-        <is>
-          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
-        </is>
-      </c>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr"/>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU7" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>8</v>
       </c>
       <c r="AV7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 12:28</t>
+          <t>2026-09-02 13:42</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>R1-PLTR-USA-20260902-1a2a27</t>
+          <t>R1-MU-USA-20260902-2ba5dc</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>PLTR_USA_20260902</t>
+          <t>MU_USA_20260902</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1728,24 +1688,24 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="n">
-        <v>79.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
@@ -1753,7 +1713,7 @@
         </is>
       </c>
       <c r="P8" s="3" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>-0.8</v>
@@ -1765,7 +1725,7 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 49% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #6 · Conf 49% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr"/>
@@ -1778,7 +1738,7 @@
         </is>
       </c>
       <c r="W8" s="3" t="n">
-        <v>67.2</v>
+        <v>48.5</v>
       </c>
       <c r="X8" s="3" t="inlineStr"/>
       <c r="Y8" s="3" t="n">
@@ -1792,40 +1752,40 @@
       </c>
       <c r="AB8" s="3" t="inlineStr"/>
       <c r="AC8" s="3" t="n">
-        <v>179.92</v>
+        <v>933.4400000000001</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>179.92</v>
+        <v>933.4400000000001</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>178.12</v>
+        <v>924.11</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>181.72</v>
+        <v>942.77</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>170.924</v>
+        <v>886.768</v>
       </c>
       <c r="AH8" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>201.51</v>
+        <v>1045.45</v>
       </c>
       <c r="AJ8" s="3" t="n">
         <v>12</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>215.6157</v>
+        <v>1118.6315</v>
       </c>
       <c r="AL8" s="3" t="n">
         <v>19.84</v>
       </c>
       <c r="AM8" s="3" t="n">
-        <v>186.38</v>
+        <v>958.73</v>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>-3.47</v>
+        <v>-2.64</v>
       </c>
       <c r="AO8" s="3" t="n">
         <v>0</v>
@@ -1850,19 +1810,19 @@
       </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 12:28</t>
+          <t>2026-09-02 13:42</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>R1-VLO-USA-20260902-678f0c</t>
+          <t>R1-MSFT-USA-20260902-880456</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>VLO_USA_20260902</t>
+          <t>MSFT_USA_20260902</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1882,24 +1842,28 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>VLO</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="3" t="n">
-        <v>80.8</v>
+        <v>81.5</v>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
@@ -1914,12 +1878,12 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 52% · momentum → · band STRONG · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 52% · momentum → · band HOLD→STRONG · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr"/>
@@ -1932,7 +1896,7 @@
         </is>
       </c>
       <c r="W9" s="3" t="n">
-        <v>59.4</v>
+        <v>48</v>
       </c>
       <c r="X9" s="3" t="inlineStr"/>
       <c r="Y9" s="3" t="n">
@@ -1946,40 +1910,40 @@
       </c>
       <c r="AB9" s="3" t="inlineStr"/>
       <c r="AC9" s="3" t="n">
-        <v>361.99</v>
+        <v>501.02</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>361.99</v>
+        <v>501.02</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>358.37</v>
+        <v>491</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>365.61</v>
+        <v>511.04</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>343.8905</v>
+        <v>475.9689999999999</v>
       </c>
       <c r="AH9" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>405.43</v>
+        <v>541.1016</v>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>433.8101</v>
+        <v>578.978712</v>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>19.84</v>
+        <v>15.56</v>
       </c>
       <c r="AM9" s="3" t="n">
-        <v>358.92</v>
+        <v>507.29</v>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>0.86</v>
+        <v>-1.24</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>0</v>
@@ -2000,23 +1964,23 @@
         <v>5</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 12:28</t>
+          <t>2026-09-02 13:42</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>R1-SNDK-USA-20260902-6a01d7</t>
+          <t>R1-HON-USA-20260902-c15300</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SNDK_USA_20260902</t>
+          <t>HON_USA_20260902</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -2036,24 +2000,28 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>SNDK</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr"/>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L10" s="3" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="3" t="n">
-        <v>72.3</v>
+        <v>72.5</v>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
@@ -2061,24 +2029,24 @@
         </is>
       </c>
       <c r="P10" s="3" t="n">
-        <v>42.3</v>
+        <v>53.8</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>-0.8</v>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #3 · Conf 43% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr"/>
       <c r="U10" s="3" t="n">
-        <v>43</v>
+        <v>54.5</v>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
@@ -2086,7 +2054,7 @@
         </is>
       </c>
       <c r="W10" s="3" t="n">
-        <v>53</v>
+        <v>47.4</v>
       </c>
       <c r="X10" s="3" t="inlineStr"/>
       <c r="Y10" s="3" t="n">
@@ -2100,40 +2068,40 @@
       </c>
       <c r="AB10" s="3" t="inlineStr"/>
       <c r="AC10" s="3" t="n">
-        <v>1536.87</v>
+        <v>209.98</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>1536.87</v>
+        <v>209.98</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>1506.13</v>
+        <v>205.78</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>1567.61</v>
+        <v>214.18</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>1460.0265</v>
+        <v>199.481</v>
       </c>
       <c r="AH10" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>1659.8196</v>
+        <v>226.7784</v>
       </c>
       <c r="AJ10" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>1776.006972</v>
+        <v>242.652888</v>
       </c>
       <c r="AL10" s="3" t="n">
         <v>15.56</v>
       </c>
       <c r="AM10" s="3" t="n">
-        <v>1566.7</v>
+        <v>213.53</v>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>-1.9</v>
+        <v>-1.66</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>0</v>
@@ -2158,19 +2126,19 @@
       </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 12:28</t>
+          <t>2026-09-02 13:42</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>R1-INCY-USA-20260902-658db3</t>
+          <t>R1-EXPD-USA-20260902-056a7c</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>INCY_USA_20260902</t>
+          <t>EXPD_USA_20260902</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2190,7 +2158,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -2202,12 +2170,12 @@
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L11" s="3" t="inlineStr"/>
       <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
@@ -2215,7 +2183,7 @@
         </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>-0.8</v>
@@ -2227,7 +2195,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 49% · momentum → · band HOLD · 91d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 49% · momentum → · band STRONG · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr"/>
@@ -2240,7 +2208,7 @@
         </is>
       </c>
       <c r="W11" s="3" t="n">
-        <v>49.3</v>
+        <v>42.5</v>
       </c>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="n">
@@ -2254,40 +2222,40 @@
       </c>
       <c r="AB11" s="3" t="inlineStr"/>
       <c r="AC11" s="3" t="n">
-        <v>125.01</v>
+        <v>187.7</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>125.01</v>
+        <v>187.7</v>
       </c>
       <c r="AE11" s="3" t="n">
-        <v>122.51</v>
+        <v>183.95</v>
       </c>
       <c r="AF11" s="3" t="n">
-        <v>127.51</v>
+        <v>191.45</v>
       </c>
       <c r="AG11" s="3" t="n">
-        <v>118.7595</v>
+        <v>178.315</v>
       </c>
       <c r="AH11" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>135.0108</v>
+        <v>202.716</v>
       </c>
       <c r="AJ11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>144.461556</v>
+        <v>216.90612</v>
       </c>
       <c r="AL11" s="3" t="n">
         <v>15.56</v>
       </c>
       <c r="AM11" s="3" t="n">
-        <v>123.22</v>
+        <v>189.65</v>
       </c>
       <c r="AN11" s="3" t="n">
-        <v>1.45</v>
+        <v>-1.03</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>0</v>
@@ -2312,19 +2280,19 @@
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 12:28</t>
+          <t>2026-09-02 13:42</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>R1-GRMN-USA-20260902-dc608d</t>
+          <t>R1-OXY-USA-20260902-67e560</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>GRMN_USA_20260902</t>
+          <t>OXY_USA_20260902</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2344,7 +2312,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -2356,12 +2324,12 @@
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L12" s="3" t="inlineStr"/>
       <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
@@ -2369,7 +2337,7 @@
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>48.1</v>
+        <v>51</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>-0.8</v>
@@ -2381,12 +2349,12 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 49% · momentum → · band HOLD · 91d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 52% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr"/>
       <c r="U12" s="3" t="n">
-        <v>48.9</v>
+        <v>51.7</v>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
@@ -2394,7 +2362,7 @@
         </is>
       </c>
       <c r="W12" s="3" t="n">
-        <v>48.7</v>
+        <v>40.6</v>
       </c>
       <c r="X12" s="3" t="inlineStr"/>
       <c r="Y12" s="3" t="n">
@@ -2408,40 +2376,40 @@
       </c>
       <c r="AB12" s="3" t="inlineStr"/>
       <c r="AC12" s="3" t="n">
-        <v>275.17</v>
+        <v>60.95</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>275.17</v>
+        <v>60.95</v>
       </c>
       <c r="AE12" s="3" t="n">
-        <v>269.67</v>
+        <v>59.73</v>
       </c>
       <c r="AF12" s="3" t="n">
-        <v>280.67</v>
+        <v>62.17</v>
       </c>
       <c r="AG12" s="3" t="n">
-        <v>261.4115</v>
+        <v>57.9025</v>
       </c>
       <c r="AH12" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>297.1836</v>
+        <v>65.82600000000001</v>
       </c>
       <c r="AJ12" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>317.986452</v>
+        <v>70.43382000000001</v>
       </c>
       <c r="AL12" s="3" t="n">
         <v>15.56</v>
       </c>
       <c r="AM12" s="3" t="n">
-        <v>284.11</v>
+        <v>60.18</v>
       </c>
       <c r="AN12" s="3" t="n">
-        <v>-3.15</v>
+        <v>1.28</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>0</v>
@@ -2466,19 +2434,19 @@
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 12:28</t>
+          <t>2026-09-02 13:42</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>R1-MU-USA-20260902-2ba5dc</t>
+          <t>R2-TRV-USA-20260810-a2c57b</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>MU_USA_20260902</t>
+          <t>TRV_USA_20260810</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2493,15 +2461,19 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>MU</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr"/>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2510,37 +2482,27 @@
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L13" s="3" t="inlineStr"/>
-      <c r="M13" s="3" t="inlineStr"/>
-      <c r="N13" s="3" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="Q13" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="R13" s="3" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #6 · Conf 49% · momentum → · band HOLD · 91d left · → HOLD</t>
+          <t>Rank → 1→1 · Conf 57% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr"/>
       <c r="U13" s="3" t="n">
-        <v>48.9</v>
+        <v>56.8</v>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
@@ -2548,91 +2510,61 @@
         </is>
       </c>
       <c r="W13" s="3" t="n">
-        <v>48.5</v>
+        <v>29.2</v>
       </c>
       <c r="X13" s="3" t="inlineStr"/>
       <c r="Y13" s="3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA13" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB13" s="3" t="inlineStr"/>
-      <c r="AC13" s="3" t="n">
-        <v>933.4400000000001</v>
-      </c>
-      <c r="AD13" s="3" t="n">
-        <v>933.4400000000001</v>
-      </c>
-      <c r="AE13" s="3" t="n">
-        <v>924.11</v>
-      </c>
-      <c r="AF13" s="3" t="n">
-        <v>942.77</v>
-      </c>
-      <c r="AG13" s="3" t="n">
-        <v>886.768</v>
-      </c>
-      <c r="AH13" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI13" s="3" t="n">
-        <v>1045.45</v>
-      </c>
-      <c r="AJ13" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK13" s="3" t="n">
-        <v>1118.6315</v>
-      </c>
-      <c r="AL13" s="3" t="n">
-        <v>19.84</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr"/>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr"/>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr"/>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr"/>
       <c r="AM13" s="3" t="n">
-        <v>958.73</v>
+        <v>365.93</v>
       </c>
       <c r="AN13" s="3" t="n">
-        <v>-2.64</v>
-      </c>
-      <c r="AO13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.55</v>
+      </c>
+      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr"/>
-      <c r="AS13" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AT13" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU13" s="3" t="n">
-        <v>12</v>
-      </c>
+      <c r="AS13" s="3" t="inlineStr"/>
+      <c r="AT13" s="3" t="inlineStr"/>
+      <c r="AU13" s="3" t="inlineStr"/>
       <c r="AV13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 12:28</t>
+          <t>2026-09-02 13:42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>R1-MSFT-USA-20260902-880456</t>
+          <t>R2-V-USA-20260810-1697f4</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MSFT_USA_20260902</t>
+          <t>V_USA_20260810</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2647,17 +2579,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -2668,37 +2600,27 @@
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr"/>
-      <c r="N14" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr"/>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 52% · momentum → · band HOLD→STRONG · 91d left · → HOLD</t>
+          <t>Rank → 2→2 · Conf 54% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="n">
-        <v>51.7</v>
+        <v>53.6</v>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
@@ -2706,786 +2628,54 @@
         </is>
       </c>
       <c r="W14" s="3" t="n">
-        <v>48</v>
+        <v>27.8</v>
       </c>
       <c r="X14" s="3" t="inlineStr"/>
       <c r="Y14" s="3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA14" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB14" s="3" t="inlineStr"/>
-      <c r="AC14" s="3" t="n">
-        <v>501.02</v>
-      </c>
-      <c r="AD14" s="3" t="n">
-        <v>501.02</v>
-      </c>
-      <c r="AE14" s="3" t="n">
-        <v>491</v>
-      </c>
-      <c r="AF14" s="3" t="n">
-        <v>511.04</v>
-      </c>
-      <c r="AG14" s="3" t="n">
-        <v>475.9689999999999</v>
-      </c>
-      <c r="AH14" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI14" s="3" t="n">
-        <v>541.1016</v>
-      </c>
-      <c r="AJ14" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK14" s="3" t="n">
-        <v>578.978712</v>
-      </c>
-      <c r="AL14" s="3" t="n">
-        <v>15.56</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr"/>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr"/>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr"/>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr"/>
       <c r="AM14" s="3" t="n">
-        <v>507.29</v>
+        <v>379.37</v>
       </c>
       <c r="AN14" s="3" t="n">
-        <v>-1.24</v>
-      </c>
-      <c r="AO14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-1.77</v>
+      </c>
+      <c r="AO14" s="3" t="inlineStr"/>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr"/>
-      <c r="AS14" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AT14" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU14" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AS14" s="3" t="inlineStr"/>
+      <c r="AT14" s="3" t="inlineStr"/>
+      <c r="AU14" s="3" t="inlineStr"/>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 12:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>R1-HON-USA-20260902-c15300</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>HON_USA_20260902</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>HON</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Honeywell</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr"/>
-      <c r="J15" s="3" t="inlineStr"/>
-      <c r="K15" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
-      <c r="N15" s="3" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T15" s="3" t="inlineStr"/>
-      <c r="U15" s="3" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="V15" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="X15" s="3" t="inlineStr"/>
-      <c r="Y15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AA15" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB15" s="3" t="inlineStr"/>
-      <c r="AC15" s="3" t="n">
-        <v>209.98</v>
-      </c>
-      <c r="AD15" s="3" t="n">
-        <v>209.98</v>
-      </c>
-      <c r="AE15" s="3" t="n">
-        <v>205.78</v>
-      </c>
-      <c r="AF15" s="3" t="n">
-        <v>214.18</v>
-      </c>
-      <c r="AG15" s="3" t="n">
-        <v>199.481</v>
-      </c>
-      <c r="AH15" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI15" s="3" t="n">
-        <v>226.7784</v>
-      </c>
-      <c r="AJ15" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK15" s="3" t="n">
-        <v>242.652888</v>
-      </c>
-      <c r="AL15" s="3" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AM15" s="3" t="n">
-        <v>213.53</v>
-      </c>
-      <c r="AN15" s="3" t="n">
-        <v>-1.66</v>
-      </c>
-      <c r="AO15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" s="3" t="inlineStr"/>
-      <c r="AS15" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AT15" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU15" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02 12:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>R1-EXPD-USA-20260902-056a7c</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>EXPD_USA_20260902</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>EXPD</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="3" t="inlineStr"/>
-      <c r="K16" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr"/>
-      <c r="N16" s="3" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="Q16" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="R16" s="3" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
-        </is>
-      </c>
-      <c r="S16" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 49% · momentum → · band STRONG · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T16" s="3" t="inlineStr"/>
-      <c r="U16" s="3" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="V16" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W16" s="3" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="X16" s="3" t="inlineStr"/>
-      <c r="Y16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AA16" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB16" s="3" t="inlineStr"/>
-      <c r="AC16" s="3" t="n">
-        <v>187.7</v>
-      </c>
-      <c r="AD16" s="3" t="n">
-        <v>187.7</v>
-      </c>
-      <c r="AE16" s="3" t="n">
-        <v>183.95</v>
-      </c>
-      <c r="AF16" s="3" t="n">
-        <v>191.45</v>
-      </c>
-      <c r="AG16" s="3" t="n">
-        <v>178.315</v>
-      </c>
-      <c r="AH16" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI16" s="3" t="n">
-        <v>202.716</v>
-      </c>
-      <c r="AJ16" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK16" s="3" t="n">
-        <v>216.90612</v>
-      </c>
-      <c r="AL16" s="3" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AM16" s="3" t="n">
-        <v>189.65</v>
-      </c>
-      <c r="AN16" s="3" t="n">
-        <v>-1.03</v>
-      </c>
-      <c r="AO16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" s="3" t="inlineStr"/>
-      <c r="AS16" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AT16" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU16" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV16" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02 12:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>R1-OXY-USA-20260902-67e560</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>OXY_USA_20260902</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>OXY</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="3" t="inlineStr"/>
-      <c r="K17" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="3" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 52% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T17" s="3" t="inlineStr"/>
-      <c r="U17" s="3" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="V17" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="X17" s="3" t="inlineStr"/>
-      <c r="Y17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AA17" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB17" s="3" t="inlineStr"/>
-      <c r="AC17" s="3" t="n">
-        <v>60.95</v>
-      </c>
-      <c r="AD17" s="3" t="n">
-        <v>60.95</v>
-      </c>
-      <c r="AE17" s="3" t="n">
-        <v>59.73</v>
-      </c>
-      <c r="AF17" s="3" t="n">
-        <v>62.17</v>
-      </c>
-      <c r="AG17" s="3" t="n">
-        <v>57.9025</v>
-      </c>
-      <c r="AH17" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI17" s="3" t="n">
-        <v>65.82600000000001</v>
-      </c>
-      <c r="AJ17" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK17" s="3" t="n">
-        <v>70.43382000000001</v>
-      </c>
-      <c r="AL17" s="3" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AM17" s="3" t="n">
-        <v>60.18</v>
-      </c>
-      <c r="AN17" s="3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AO17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" s="3" t="inlineStr"/>
-      <c r="AS17" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AT17" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU17" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02 12:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>R2-TRV-USA-20260810-a2c57b</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>TRV_USA_20260810</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>TRV</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Travelers</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr"/>
-      <c r="J18" s="3" t="inlineStr"/>
-      <c r="K18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="3" t="inlineStr"/>
-      <c r="O18" s="3" t="inlineStr"/>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="3" t="inlineStr"/>
-      <c r="R18" s="3" t="inlineStr"/>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t>Rank → 1→1 · Conf 57% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T18" s="3" t="inlineStr"/>
-      <c r="U18" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="V18" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W18" s="3" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="X18" s="3" t="inlineStr"/>
-      <c r="Y18" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z18" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA18" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB18" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AC18" s="3" t="inlineStr"/>
-      <c r="AD18" s="3" t="inlineStr"/>
-      <c r="AE18" s="3" t="inlineStr"/>
-      <c r="AF18" s="3" t="inlineStr"/>
-      <c r="AG18" s="3" t="inlineStr"/>
-      <c r="AH18" s="3" t="inlineStr"/>
-      <c r="AI18" s="3" t="inlineStr"/>
-      <c r="AJ18" s="3" t="inlineStr"/>
-      <c r="AK18" s="3" t="inlineStr"/>
-      <c r="AL18" s="3" t="inlineStr"/>
-      <c r="AM18" s="3" t="n">
-        <v>365.93</v>
-      </c>
-      <c r="AN18" s="3" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="AO18" s="3" t="inlineStr"/>
-      <c r="AP18" s="3" t="inlineStr"/>
-      <c r="AQ18" s="3" t="inlineStr"/>
-      <c r="AR18" s="3" t="inlineStr"/>
-      <c r="AS18" s="3" t="inlineStr"/>
-      <c r="AT18" s="3" t="inlineStr"/>
-      <c r="AU18" s="3" t="inlineStr"/>
-      <c r="AV18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02 12:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>R2-V-USA-20260810-1697f4</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>V_USA_20260810</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
-      <c r="K19" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr"/>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="inlineStr"/>
-      <c r="R19" s="3" t="inlineStr"/>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t>Rank → 2→2 · Conf 54% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T19" s="3" t="inlineStr"/>
-      <c r="U19" s="3" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W19" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="X19" s="3" t="inlineStr"/>
-      <c r="Y19" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z19" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA19" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB19" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AC19" s="3" t="inlineStr"/>
-      <c r="AD19" s="3" t="inlineStr"/>
-      <c r="AE19" s="3" t="inlineStr"/>
-      <c r="AF19" s="3" t="inlineStr"/>
-      <c r="AG19" s="3" t="inlineStr"/>
-      <c r="AH19" s="3" t="inlineStr"/>
-      <c r="AI19" s="3" t="inlineStr"/>
-      <c r="AJ19" s="3" t="inlineStr"/>
-      <c r="AK19" s="3" t="inlineStr"/>
-      <c r="AL19" s="3" t="inlineStr"/>
-      <c r="AM19" s="3" t="n">
-        <v>379.37</v>
-      </c>
-      <c r="AN19" s="3" t="n">
-        <v>-1.77</v>
-      </c>
-      <c r="AO19" s="3" t="inlineStr"/>
-      <c r="AP19" s="3" t="inlineStr"/>
-      <c r="AQ19" s="3" t="inlineStr"/>
-      <c r="AR19" s="3" t="inlineStr"/>
-      <c r="AS19" s="3" t="inlineStr"/>
-      <c r="AT19" s="3" t="inlineStr"/>
-      <c r="AU19" s="3" t="inlineStr"/>
-      <c r="AV19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02 12:28</t>
+          <t>2026-09-02 13:42</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV19"/>
+  <autoFilter ref="A1:AV14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>